--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:12:38+00:00</t>
+    <t>2026-09-14T19:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -139,7 +139,7 @@
     <t>48676-1</t>
   </si>
   <si>
-    <t>HER2 [Interpretation] in Tissue</t>
+    <t>HER2 Ag [Interpretation] in Tissue</t>
   </si>
   <si>
     <t>85319-2</t>
@@ -199,25 +199,25 @@
     <t>81691-8</t>
   </si>
   <si>
-    <t>DNA mismatch repair protein Mlh1 [Presence] in Cancer specimen by Immune stain</t>
+    <t>MLH-1 Ag [Presence] in Cancer specimen by Immune stain</t>
   </si>
   <si>
     <t>81692-6</t>
   </si>
   <si>
-    <t>DNA mismatch repair protein Msh2 [Presence] in Cancer specimen by Immune stain</t>
+    <t>MSH-2 Ag [Presence] in Cancer specimen by Immune stain</t>
   </si>
   <si>
     <t>81693-4</t>
   </si>
   <si>
-    <t>DNA mismatch repair protein Msh6 [Presence] in Cancer specimen by Immune stain</t>
+    <t>MSH-6 Ag [Presence] in Cancer specimen by Immune stain</t>
   </si>
   <si>
     <t>81694-2</t>
   </si>
   <si>
-    <t>Mismatch repair endonuclease PMS2 [Presence] in Cancer specimen by Immune stain</t>
+    <t>PMS2 Ag [Presence] in Cancer specimen by Immune stain</t>
   </si>
   <si>
     <t>14229-9</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:45:33+00:00</t>
+    <t>2026-09-14T20:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:15:28+00:00</t>
+    <t>2026-09-14T20:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:43:02+00:00</t>
+    <t>2026-09-14T21:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:08:50+00:00</t>
+    <t>2026-09-14T21:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:38:27+00:00</t>
+    <t>2026-09-14T22:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-immunohistochemistry-specific-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:18:02+00:00</t>
+    <t>2026-09-14T22:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
